--- a/results/rna_atac_integration/I315RvI315X_rna_atac_plot_raw_data.xlsx
+++ b/results/rna_atac_integration/I315RvI315X_rna_atac_plot_raw_data.xlsx
@@ -496,10 +496,10 @@
         </is>
       </c>
       <c r="P2">
-        <v>4.938809132262872</v>
+        <v>5.079019104408325</v>
       </c>
       <c r="Q2">
-        <v>0.0072525532177096</v>
+        <v>2.04261375221268E-15</v>
       </c>
     </row>
     <row r="3">
@@ -557,10 +557,10 @@
         </is>
       </c>
       <c r="P3">
-        <v>2.481254624897814</v>
+        <v>2.481299765734046</v>
       </c>
       <c r="Q3">
-        <v>0.0225132289455906</v>
+        <v>0.02352403769734551</v>
       </c>
     </row>
     <row r="4">
@@ -618,10 +618,10 @@
         </is>
       </c>
       <c r="P4">
-        <v>4.661976251554973</v>
+        <v>4.66197992540449</v>
       </c>
       <c r="Q4">
-        <v>5.906335303814449E-38</v>
+        <v>8.40919541813414E-38</v>
       </c>
     </row>
     <row r="5">
@@ -679,10 +679,10 @@
         </is>
       </c>
       <c r="P5">
-        <v>2.810996471287302</v>
+        <v>2.810981928942583</v>
       </c>
       <c r="Q5">
-        <v>3.646246731757675E-10</v>
+        <v>4.139616499682949E-10</v>
       </c>
     </row>
     <row r="6">
@@ -740,10 +740,10 @@
         </is>
       </c>
       <c r="P6">
-        <v>2.011466004289944</v>
+        <v>2.01145694734304</v>
       </c>
       <c r="Q6">
-        <v>4.142493627082923E-10</v>
+        <v>4.32063551747694E-10</v>
       </c>
     </row>
     <row r="7">
@@ -801,10 +801,10 @@
         </is>
       </c>
       <c r="P7">
-        <v>2.481254624897814</v>
+        <v>2.481299765734046</v>
       </c>
       <c r="Q7">
-        <v>0.0225132289455906</v>
+        <v>0.02352403769734551</v>
       </c>
     </row>
     <row r="8">
@@ -862,10 +862,10 @@
         </is>
       </c>
       <c r="P8">
-        <v>1.727650788129317</v>
+        <v>1.727653232161164</v>
       </c>
       <c r="Q8">
-        <v>0.005967758923280671</v>
+        <v>0.006189448402069572</v>
       </c>
     </row>
     <row r="9">
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="P9">
-        <v>1.87801038332146</v>
+        <v>1.877969799722331</v>
       </c>
       <c r="Q9">
-        <v>0.001001069155878194</v>
+        <v>0.001046858805441891</v>
       </c>
     </row>
     <row r="10">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="P10">
-        <v>1.459379493305387</v>
+        <v>1.459354926854977</v>
       </c>
       <c r="Q10">
-        <v>0.005967758923280671</v>
+        <v>0.006153947128357157</v>
       </c>
     </row>
     <row r="11">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="P11">
-        <v>1.142054705548562</v>
+        <v>1.142055442343811</v>
       </c>
       <c r="Q11">
-        <v>5.922397797589096E-05</v>
+        <v>5.675132464358469E-05</v>
       </c>
     </row>
     <row r="12">
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="P12">
-        <v>2.979864675063563</v>
+        <v>2.979722036402269</v>
       </c>
       <c r="Q12">
-        <v>0.003034138766013878</v>
+        <v>0.003130315906331423</v>
       </c>
     </row>
     <row r="13">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="P13">
-        <v>1.597130057778551</v>
+        <v>1.597142359573084</v>
       </c>
       <c r="Q13">
-        <v>5.813232898484706E-05</v>
+        <v>6.002837336065364E-05</v>
       </c>
     </row>
     <row r="14">
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="P14">
-        <v>2.586162904635926</v>
+        <v>2.586049324884496</v>
       </c>
       <c r="Q14">
-        <v>0.0002093760450183027</v>
+        <v>0.000222663745060704</v>
       </c>
     </row>
     <row r="15">
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="P15">
-        <v>2.152885851763551</v>
+        <v>2.152888964094629</v>
       </c>
       <c r="Q15">
-        <v>1.767702616480132E-10</v>
+        <v>1.888106771431818E-10</v>
       </c>
     </row>
     <row r="16">
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="P16">
-        <v>4.661976251554973</v>
+        <v>4.66197992540449</v>
       </c>
       <c r="Q16">
-        <v>5.906335303814449E-38</v>
+        <v>8.40919541813414E-38</v>
       </c>
     </row>
     <row r="17">
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="P17">
-        <v>1.997211832051237</v>
+        <v>1.997030698406669</v>
       </c>
       <c r="Q17">
-        <v>0.02505385608806695</v>
+        <v>0.02575912313593065</v>
       </c>
     </row>
     <row r="18">
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="P18">
-        <v>2.554827070349844</v>
+        <v>2.553327702235356</v>
       </c>
       <c r="Q18">
-        <v>0.01238253081756086</v>
+        <v>0.01285729695513689</v>
       </c>
     </row>
     <row r="19">
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="P19">
-        <v>1.87801038332146</v>
+        <v>1.877969799722331</v>
       </c>
       <c r="Q19">
-        <v>0.001001069155878194</v>
+        <v>0.001046858805441891</v>
       </c>
     </row>
     <row r="20">
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="P20">
-        <v>1.101306728838127</v>
+        <v>1.101303241731588</v>
       </c>
       <c r="Q20">
-        <v>0.005371418757231774</v>
+        <v>0.005409410146722616</v>
       </c>
     </row>
     <row r="21">
@@ -1655,10 +1655,10 @@
         </is>
       </c>
       <c r="P21">
-        <v>1.575367547643594</v>
+        <v>1.575367521659543</v>
       </c>
       <c r="Q21">
-        <v>5.795972555727818E-11</v>
+        <v>5.657862329467875E-11</v>
       </c>
     </row>
     <row r="22">
@@ -1716,10 +1716,10 @@
         </is>
       </c>
       <c r="P22">
-        <v>1.758848687542044</v>
+        <v>1.758849220287323</v>
       </c>
       <c r="Q22">
-        <v>1.370608235022969E-18</v>
+        <v>1.211084096590472E-18</v>
       </c>
     </row>
     <row r="23">
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="P23">
-        <v>2.481254624897814</v>
+        <v>2.481299765734046</v>
       </c>
       <c r="Q23">
-        <v>0.0225132289455906</v>
+        <v>0.02352403769734551</v>
       </c>
     </row>
     <row r="24">
@@ -1838,10 +1838,10 @@
         </is>
       </c>
       <c r="P24">
-        <v>2.543136991827881</v>
+        <v>2.543121322469782</v>
       </c>
       <c r="Q24">
-        <v>1.121054787582716E-16</v>
+        <v>1.152234360617388E-16</v>
       </c>
     </row>
     <row r="25">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="P25">
-        <v>2.481254624897814</v>
+        <v>2.481299765734046</v>
       </c>
       <c r="Q25">
-        <v>0.0225132289455906</v>
+        <v>0.02352403769734551</v>
       </c>
     </row>
     <row r="26">
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="P26">
-        <v>2.333176361812052</v>
+        <v>2.333184554562516</v>
       </c>
       <c r="Q26">
-        <v>7.403880567003414E-10</v>
+        <v>8.329756890246816E-10</v>
       </c>
     </row>
     <row r="27">
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="P27">
-        <v>3.208081400977774</v>
+        <v>3.208089043665391</v>
       </c>
       <c r="Q27">
-        <v>2.449293444119983E-09</v>
+        <v>2.819416229304328E-09</v>
       </c>
     </row>
     <row r="28">
@@ -2082,10 +2082,10 @@
         </is>
       </c>
       <c r="P28">
-        <v>2.7836981338123</v>
+        <v>2.783698167883029</v>
       </c>
       <c r="Q28">
-        <v>6.139215198199052E-24</v>
+        <v>7.731373072131922E-24</v>
       </c>
     </row>
     <row r="29">
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="P29">
-        <v>2.481254624897814</v>
+        <v>2.481299765734046</v>
       </c>
       <c r="Q29">
-        <v>0.0225132289455906</v>
+        <v>0.02352403769734551</v>
       </c>
     </row>
     <row r="30">
@@ -2204,10 +2204,10 @@
         </is>
       </c>
       <c r="P30">
-        <v>1.077283253984746</v>
+        <v>1.077283886191586</v>
       </c>
       <c r="Q30">
-        <v>2.577092260082622E-06</v>
+        <v>2.375535197657737E-06</v>
       </c>
     </row>
     <row r="31">
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="P31">
-        <v>1.597130057778551</v>
+        <v>1.597142359573084</v>
       </c>
       <c r="Q31">
-        <v>5.813232898484706E-05</v>
+        <v>6.002837336065364E-05</v>
       </c>
     </row>
     <row r="32">
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="P32">
-        <v>3.158782804333514</v>
+        <v>3.158771851394899</v>
       </c>
       <c r="Q32">
-        <v>2.452525700556116E-10</v>
+        <v>2.816805311506383E-10</v>
       </c>
     </row>
     <row r="33">
@@ -2387,10 +2387,10 @@
         </is>
       </c>
       <c r="P33">
-        <v>2.333176361812052</v>
+        <v>2.333184554562516</v>
       </c>
       <c r="Q33">
-        <v>7.403880567003414E-10</v>
+        <v>8.329756890246816E-10</v>
       </c>
     </row>
     <row r="34">
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="P34">
-        <v>1.195057698062226</v>
+        <v>1.195058587256469</v>
       </c>
       <c r="Q34">
-        <v>5.922397797589096E-05</v>
+        <v>5.675132464358469E-05</v>
       </c>
     </row>
     <row r="35">
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="P35">
-        <v>2.333176361812052</v>
+        <v>2.333184554562516</v>
       </c>
       <c r="Q35">
-        <v>7.403880567003414E-10</v>
+        <v>8.329756890246816E-10</v>
       </c>
     </row>
     <row r="36">
@@ -2570,10 +2570,10 @@
         </is>
       </c>
       <c r="P36">
-        <v>1.947788468442436</v>
+        <v>1.947736496580502</v>
       </c>
       <c r="Q36">
-        <v>3.478338008584465E-07</v>
+        <v>3.644620732343786E-07</v>
       </c>
     </row>
     <row r="37">
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="P37">
-        <v>2.543136991827881</v>
+        <v>2.543121322469782</v>
       </c>
       <c r="Q37">
-        <v>1.121054787582716E-16</v>
+        <v>1.152234360617388E-16</v>
       </c>
     </row>
     <row r="38">
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="P38">
-        <v>2.481254624897814</v>
+        <v>2.481299765734046</v>
       </c>
       <c r="Q38">
-        <v>0.0225132289455906</v>
+        <v>0.02352403769734551</v>
       </c>
     </row>
   </sheetData>
